--- a/胎壓偵測/HYUNDAI_Data.xlsx
+++ b/胎壓偵測/HYUNDAI_Data.xlsx
@@ -29111,10 +29111,26 @@
           <t>AER</t>
         </is>
       </c>
-      <c r="G656" t="inlineStr"/>
-      <c r="H656" t="inlineStr"/>
-      <c r="I656" t="inlineStr"/>
-      <c r="J656" t="inlineStr"/>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>08/2017 -</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>TG1C | 2910000102400 (Ident: 2910000102300)</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>VDO</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -29635,10 +29651,26 @@
           <t>AES</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr"/>
-      <c r="H667" t="inlineStr"/>
-      <c r="I667" t="inlineStr"/>
-      <c r="J667" t="inlineStr"/>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>08/2017 -</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>TG1C | 2910000102400 (Ident: 2910000102300)</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>VDO</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -31295,10 +31327,26 @@
           <t>AFK</t>
         </is>
       </c>
-      <c r="G702" t="inlineStr"/>
-      <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr"/>
-      <c r="J702" t="inlineStr"/>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>08/2017 -</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>TG1C | 2910000102400 (Ident: 2910000102300)</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>VDO</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
